--- a/translators/xlsx/tests/sample.xlsx
+++ b/translators/xlsx/tests/sample.xlsx
@@ -17,6 +17,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="3" max="4" width="8" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1">

--- a/translators/xlsx/tests/sample.xlsx
+++ b/translators/xlsx/tests/sample.xlsx
@@ -15,6 +15,99 @@
 </sst>
 </file>
 
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
+  </fonts>
+  <fills count="3">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+  </cellXfs>
+</styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <a:themeElements>
+    <a:clrScheme name="Test">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
@@ -23,10 +116,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1">
+      <c r="A1" s="1">
         <v>15</v>
       </c>
-      <c r="B1">
+      <c r="B1" s="2">
         <v>25</v>
       </c>
       <c r="C1">

--- a/translators/xlsx/tests/sample.xlsx
+++ b/translators/xlsx/tests/sample.xlsx
@@ -115,7 +115,7 @@
     <col min="3" max="4" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1">
         <v>15</v>
       </c>

--- a/translators/xlsx/tests/sample.xlsx
+++ b/translators/xlsx/tests/sample.xlsx
@@ -110,6 +110,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="3" max="4" width="8" customWidth="1"/>

--- a/translators/xlsx/tests/sample.xlsx
+++ b/translators/xlsx/tests/sample.xlsx
@@ -133,6 +133,8 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2" hidden="1"/>
   </sheetData>
+  <autoFilter ref="A1:D1"/>
 </worksheet>
 </file>
--- a/translators/xlsx/tests/sample.xlsx
+++ b/translators/xlsx/tests/sample.xlsx
@@ -19,12 +19,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="2">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
     </font>
